--- a/output/graficos_dimensiones/comunal_migracion_flujos_od_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_migracion_flujos_od_2020_biobio.xlsx
@@ -675,7 +675,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 09:29</t>
+    <t xml:space="preserve">2026-09-18 14:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_migracion_flujos_od_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_migracion_flujos_od_2020_biobio.xlsx
@@ -126,7 +126,7 @@
     <t xml:space="preserve">72</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">55</t>
@@ -138,7 +138,7 @@
     <t xml:space="preserve">24</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">447</t>
@@ -675,7 +675,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:09</t>
+    <t xml:space="preserve">2026-10-05 04:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
